--- a/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="504">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1363,6 +1363,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
@@ -7380,7 +7384,7 @@
         <v>424</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>425</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7395,7 +7399,7 @@
         <v>415</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7403,10 +7407,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7432,10 +7436,10 @@
         <v>421</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7486,7 +7490,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7498,7 +7502,7 @@
         <v>424</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>425</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7513,7 +7517,7 @@
         <v>415</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7521,10 +7525,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7550,10 +7554,10 @@
         <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7583,10 +7587,10 @@
         <v>340</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7604,7 +7608,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7631,7 +7635,7 @@
         <v>415</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7639,10 +7643,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7668,16 +7672,16 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7705,10 +7709,10 @@
         <v>248</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7726,7 +7730,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7747,10 +7751,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>355</v>
@@ -7761,10 +7765,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7790,16 +7794,16 @@
         <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7827,10 +7831,10 @@
         <v>260</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7848,7 +7852,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7869,10 +7873,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>355</v>
@@ -7883,10 +7887,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7909,17 +7913,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7968,7 +7972,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7995,7 +7999,7 @@
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8003,10 +8007,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8029,13 +8033,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8086,7 +8090,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8113,7 +8117,7 @@
         <v>415</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8121,10 +8125,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8147,16 +8151,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8206,7 +8210,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8230,7 +8234,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>209</v>
@@ -8241,10 +8245,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8267,16 +8271,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8326,7 +8330,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8350,10 +8354,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8361,10 +8365,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8390,16 +8394,16 @@
         <v>186</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8448,7 +8452,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8472,10 +8476,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8483,10 +8487,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8601,10 +8605,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8721,10 +8725,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8843,10 +8847,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8872,13 +8876,13 @@
         <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>258</v>
@@ -8930,7 +8934,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>94</v>
@@ -8951,7 +8955,7 @@
         <v>265</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>267</v>
@@ -8965,10 +8969,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8991,16 +8995,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>327</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>329</v>
@@ -9052,7 +9056,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9073,7 +9077,7 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>332</v>
@@ -9087,10 +9091,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9116,13 +9120,13 @@
         <v>243</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>339</v>
@@ -9174,7 +9178,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9209,10 +9213,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9296,7 +9300,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9331,10 +9335,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9360,10 +9364,10 @@
         <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>412</v>
@@ -9418,7 +9422,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-systolic-blood-pressure-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
